--- a/GEO/methylation/metadata_methylation.xlsx
+++ b/GEO/methylation/metadata_methylation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,730 +451,305 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#   together; a Series cannot mix an array platform with a sequencing platform.</t>
+          <t>#   together, one SubSeries per assay.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t># SAMPLE NAMES: three pieces carry two names, because two facilities named the same animals differently.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>STUDY</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#   The array side (this submission, the chip, the core's sheet) says IL70B, IL71B, N2. The RNA side</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>*title</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DNA methylation profiling of U251N orthotopic glioblastoma xenografts in athymic RNU/RNU rats before and after MRI-guided laser interstitial thermal therapy (LITT)</t>
+          <t>#   (GSE338105, SRA, the sequencing core's file names) says NL70B, NL71B, N269B. Neither is renamed. The</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>*summary (abstract)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Companion DNA methylation dataset to GSE338105. Laser interstitial thermal therapy (LITT) is increasingly used for deep-seated and recurrent glioblastoma. Because the graft is human and the host is rat, every array probe can be assigned to tumour or host by sequence, so the tumour compartment of a regrowing lesion is measured rather than estimated. Eight Illumina Infinium MethylationEPIC arrays were run on one chip: the six orthotopic tumours that were also sequenced (three untreated, three regrown after LITT), the contralateral hemisphere of one tumour-bearing animal, and the parental U251N culture. The arrays support copy-number, MGMT-STP27 and tumour-fraction readouts, and are reported with the matched RNA libraries.</t>
+          <t>#   pairing is stated per sample below and in the deposited multiomics_sample_key.tsv.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>*experimental design</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Eight arrays on a single EPIC BeadChip (sentrix 205648300021, positions R01C01-R08C01), scanned 2026-04-07. Six tumours: primary/pre-LITT (IL67B, IL68B, IL69B) against recurrent/post-LITT (IL66B, IL70B, IL71B; the matched RNA libraries are named NL70B and NL71B). One contralateral hemisphere (N2; RNA library N269B) and one in vitro parental culture (C2B). Each array has a matched RNA-seq library in GSE338105; DNA and RNA were taken from different aliquots of the same piece. No probe reached genome-wide significance between arms; the arrays are reported for copy number, MGMT status and tumour fraction.</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Gregory,J,Schwing</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>STUDY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>*title</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indrani,,Datta</t>
+          <t>DNA methylation profiling of U251N orthotopic glioblastoma xenografts in athymic RNU/RNU rats before and after MRI-guided laser interstitial thermal therapy (LITT)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>*summary (abstract)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tavarekere,,Nagaraja</t>
+          <t>Companion DNA methylation dataset to GSE338105. Laser interstitial thermal therapy (LITT) is increasingly used for deep-seated and recurrent glioblastoma. Because the graft is human and the host is rat, every array probe can be assigned to tumour or host by sequence, so the tumour compartment of a regrowing lesion is measured rather than estimated. Eight Illumina Infinium MethylationEPIC arrays were run on one chip: the six orthotopic tumours that were also sequenced (three untreated, three regrown after LITT), the contralateral hemisphere of one tumour-bearing animal, and the parental U251N culture. The arrays support copy-number, MGMT-STP27 and tumour-fraction readouts, and are reported with the matched RNA libraries. Every array here has a matched RNA-seq library in GSE338105, taken from a different aliquot of the same piece of tissue; the pairing is given per sample and in the supplementary file multiomics_sample_key.tsv. Three pieces carry a different name in each arm because two facilities named the same animals differently: arrays IL70B, IL71B and N2 are RNA libraries NL70B, NL71B and N269B respectively. The remaining five (IL66B, IL67B, IL68B, IL69B, C2B) carry the same name in both arms. Two RNA libraries in GSE338105 have no array in this Series (IL64B and N168B).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>*experimental design</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ian,,Lee</t>
+          <t>Eight arrays on a single EPIC BeadChip (sentrix 205648300021, positions R01C01-R08C01), scanned 2026-04-07. Six tumours: primary/pre-LITT (IL67B, IL68B, IL69B) against recurrent/post-LITT (IL66B, IL70B, IL71B; the matched RNA libraries are named NL70B and NL71B). One contralateral hemisphere (N2; RNA library N269B) and one in vitro parental culture (C2B). Each array has a matched RNA-seq library in GSE338105; DNA and RNA were taken from different aliquots of the same piece. No probe reached genome-wide significance between arms; the arrays are reported for copy number, MGMT status and tumour fraction.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>supplementary file</t>
+          <t>contributor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz</t>
+          <t>Gregory,J,Schwing</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Indrani,,Datta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tavarekere,,Nagaraja</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ian,,Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>supplementary file</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>U251N_EPIC_detection_pvalues.tsv.gz</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>SAMPLES</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>*Sample name</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>*title</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>*source name</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>*organism</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: rat</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: arm</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: tissue</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: cell line</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: treatment</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: sentrix id</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: sentrix position</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: matched RNA library</t>
-        </is>
-      </c>
-      <c r="M19" s="1" t="inlineStr">
-        <is>
-          <t>characteristics: matched RNA GEO sample</t>
-        </is>
-      </c>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>*molecule</t>
-        </is>
-      </c>
-      <c r="O19" s="1" t="inlineStr">
-        <is>
-          <t>*description</t>
-        </is>
-      </c>
-      <c r="P19" s="1" t="inlineStr">
-        <is>
-          <t>*platform</t>
-        </is>
-      </c>
-      <c r="Q19" s="1" t="inlineStr">
-        <is>
-          <t>raw file: Grn</t>
-        </is>
-      </c>
-      <c r="R19" s="1" t="inlineStr">
-        <is>
-          <t>raw file: Red</t>
-        </is>
-      </c>
-      <c r="S19" s="1" t="inlineStr">
-        <is>
-          <t>processed data file</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IL66B_EPIC</t>
+          <t>supplementary file</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U251N recurrent DNA methylation [IL66B]</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>brain (orthotopic xenograft)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Homo sapiens; Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Recurrent</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>recurrent tumour after LITT</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>U251N</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>MRI-guided laser interstitial thermal therapy (LITT), harvested at MRI-confirmed regrowth</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>205648300021</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>R01C01</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>IL66B</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>GSM9866611</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>genomic DNA</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library IL66B in GSE338105 (GSM9866611); 29.44 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>205648300021_R01C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>205648300021_R01C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz</t>
+          <t>U251N_EPIC_detection_pvalues.tsv.gz</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IL67B_EPIC</t>
+          <t>supplementary file</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U251N primary DNA methylation [IL67B]</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>brain (orthotopic xenograft)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Homo sapiens; Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>tumour (not ablated)</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>U251N</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>none (U251N implanted, not ablated)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>205648300021</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>R02C01</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>IL67B</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>GSM9866608</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>genomic DNA</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library IL67B in GSE338105 (GSM9866608); 42.52 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>205648300021_R02C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>205648300021_R02C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz</t>
+          <t>multiomics_sample_key.tsv</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>IL68B_EPIC</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U251N primary DNA methylation [IL68B]</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>brain (orthotopic xenograft)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Homo sapiens; Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>tumour (not ablated)</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>U251N</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>none (U251N implanted, not ablated)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>205648300021</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>R03C01</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>IL68B</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>GSM9866609</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>genomic DNA</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library IL68B in GSE338105 (GSM9866609); 45.38 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>205648300021_R03C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>205648300021_R03C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>IL69B_EPIC</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U251N primary DNA methylation [IL69B]</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>brain (orthotopic xenograft)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Homo sapiens; Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>tumour (not ablated)</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>U251N</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>none (U251N implanted, not ablated)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>205648300021</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>R04C01</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>IL69B</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>GSM9866610</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>genomic DNA</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library IL69B in GSE338105 (GSM9866610); 64.40 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>205648300021_R04C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>205648300021_R04C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz</t>
-        </is>
-      </c>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SAMPLES</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>IL70B_EPIC</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>U251N recurrent DNA methylation [IL70B]</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>brain (orthotopic xenograft)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Homo sapiens; Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Recurrent</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>recurrent tumour after LITT</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>U251N</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>MRI-guided laser interstitial thermal therapy (LITT), harvested at MRI-confirmed regrowth</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>205648300021</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>R05C01</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>NL70B</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>GSM9866612</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>genomic DNA</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library NL70B in GSE338105 (GSM9866612); 42.67 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>205648300021_R05C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>205648300021_R05C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>*Sample name</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>*title</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>*source name</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>*organism</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: rat</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: arm</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: tissue</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: cell line</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: treatment</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: sentrix id</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: sentrix position</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: matched RNA library</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: matched RNA GEO sample</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: matched RNA SRA experiment</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: matched RNA BioSample</t>
+        </is>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: matched RNA series</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: array label on the core sheet</t>
+        </is>
+      </c>
+      <c r="R24" s="1" t="inlineStr">
+        <is>
+          <t>*molecule</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>*description</t>
+        </is>
+      </c>
+      <c r="T24" s="1" t="inlineStr">
+        <is>
+          <t>*platform</t>
+        </is>
+      </c>
+      <c r="U24" s="1" t="inlineStr">
+        <is>
+          <t>raw file: Grn</t>
+        </is>
+      </c>
+      <c r="V24" s="1" t="inlineStr">
+        <is>
+          <t>raw file: Red</t>
+        </is>
+      </c>
+      <c r="W24" s="1" t="inlineStr">
+        <is>
+          <t>processed data file</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IL71B_EPIC</t>
+          <t>IL66B_EPIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U251N recurrent DNA methylation [IL71B]</t>
+          <t>U251N recurrent DNA methylation [IL66B]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1189,7 +764,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1219,45 +794,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>R06C01</t>
+          <t>R01C01</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>NL71B</t>
+          <t>IL66B</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>GSM9866613</t>
+          <t>GSM9866611</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t>SRX34236538</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>SAMN61491945</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>IL66B</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library NL71B in GSE338105 (GSM9866613); 33.05 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL66B in GSE338105 (GSM9866611, SRX34236538, BioSample SAMN61491945). 29.44 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>205648300021_R06C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>205648300021_R06C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>205648300021_R01C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>205648300021_R01C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1266,17 +861,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>N2_EPIC</t>
+          <t>IL67B_EPIC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U251N contralateral DNA methylation [N2]</t>
+          <t>U251N primary DNA methylation [IL67B]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>brain, contralateral hemisphere</t>
+          <t>brain (orthotopic xenograft)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1286,17 +881,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Contralateral</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>contralateral hemisphere of rat 69 (sheet: 69B control N2)</t>
+          <t>tumour (not ablated)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1306,7 +901,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>none (U251N implanted in the opposite hemisphere)</t>
+          <t>none (U251N implanted, not ablated)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1316,45 +911,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>R07C01</t>
+          <t>R02C01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>N269B</t>
+          <t>IL67B</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>GSM9866607</t>
+          <t>GSM9866608</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>SRX34236535</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>SAMN61491948</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>IL67B</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library N269B in GSE338105 (GSM9866607); 4.90 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL67B in GSE338105 (GSM9866608, SRX34236535, BioSample SAMN61491948). 42.52 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>205648300021_R07C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>205648300021_R07C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>205648300021_R02C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>205648300021_R02C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1363,33 +978,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C2B_EPIC</t>
+          <t>IL68B_EPIC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U251N culture DNA methylation [C2B]</t>
+          <t>U251N primary DNA methylation [IL68B]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>in vitro cell culture</t>
+          <t>brain (orthotopic xenograft)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Homo sapiens; Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>U251N cultured cells (parental line)</t>
+          <t>tumour (not ablated)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1399,7 +1018,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>none (in vitro reference)</t>
+          <t>none (U251N implanted, not ablated)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1409,191 +1028,796 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>R08C01</t>
+          <t>R03C01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>C2B</t>
+          <t>IL68B</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>GSM9866604</t>
+          <t>GSM9866609</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t>SRX34236536</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>SAMN61491947</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>IL68B</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Matched RNA-seq library C2B in GSE338105 (GSM9866604); 86.19 % of that library's reads were assigned human.</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL68B in GSE338105 (GSM9866609, SRX34236536, BioSample SAMN61491947). 45.38 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>205648300021_R08C01_Grn.idat</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>205648300021_R08C01_Red.idat</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>205648300021_R03C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>205648300021_R03C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IL69B_EPIC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>U251N primary DNA methylation [IL69B]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>brain (orthotopic xenograft)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Homo sapiens; Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tumour (not ablated)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>U251N</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>none (U251N implanted, not ablated)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>205648300021</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>R04C01</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>IL69B</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>GSM9866610</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SRX34236537</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>SAMN61491946</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>IL69B</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>genomic DNA</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL69B in GSE338105 (GSM9866610, SRX34236537, BioSample SAMN61491946). 64.40 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>205648300021_R04C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>205648300021_R04C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>PROTOCOLS</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n"/>
-      <c r="C29" s="1" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n"/>
-      <c r="F29" s="1" t="n"/>
-      <c r="G29" s="1" t="n"/>
-      <c r="H29" s="1" t="n"/>
-      <c r="I29" s="1" t="n"/>
-      <c r="J29" s="1" t="n"/>
-      <c r="K29" s="1" t="n"/>
-      <c r="L29" s="1" t="n"/>
-      <c r="M29" s="1" t="n"/>
-      <c r="N29" s="1" t="n"/>
-      <c r="O29" s="1" t="n"/>
-      <c r="P29" s="1" t="n"/>
-      <c r="Q29" s="1" t="n"/>
-      <c r="R29" s="1" t="n"/>
-      <c r="S29" s="1" t="n"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IL70B_EPIC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>U251N recurrent DNA methylation [IL70B = RNA library NL70B]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>brain (orthotopic xenograft)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Homo sapiens; Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recurrent</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>recurrent tumour after LITT</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>U251N</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MRI-guided laser interstitial thermal therapy (LITT), harvested at MRI-confirmed regrowth</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>205648300021</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>R05C01</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NL70B</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>GSM9866612</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SRX34236539</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>SAMN61491944</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>IL70B</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>genomic DNA</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library NL70B in GSE338105 (GSM9866612, SRX34236539, BioSample SAMN61491944). This array is named IL70B on the core's sample sheet and its RNA library is named NL70B: the same piece under two names, because the array core and the sequencing core named the animals differently. Neither name has been changed. 42.67 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>205648300021_R05C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>205648300021_R05C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>growth protocol</t>
+          <t>IL71B_EPIC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adult female immune-compromised RNU/RNU rats (Charles River Laboratories) were stereotactically implanted intracerebrally with log-growth-phase U251N human glioblastoma cells (5 x 10^4 cells in 10 uL PBS) under isoflurane anesthesia. A burr hole was drilled 3.50 mm right of bregma (anterio-posterior 0.0); cells were injected at a depth of 2.5 mm at 0.5 uL/10 s and the needle held in place 5 min before withdrawal. IACUC #1509. Tumor establishment was confirmed by MRI/DCE-MRI ~2 weeks after implantation. Eight implanted rats (64 to 71) contributed to this series.</t>
+          <t>U251N recurrent DNA methylation [IL71B = RNA library NL71B]</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>brain (orthotopic xenograft)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Homo sapiens; Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Recurrent</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>recurrent tumour after LITT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>U251N</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MRI-guided laser interstitial thermal therapy (LITT), harvested at MRI-confirmed regrowth</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>205648300021</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>R06C01</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NL71B</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>GSM9866613</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SRX34236540</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>SAMN61491943</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>IL71B</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>genomic DNA</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library NL71B in GSE338105 (GSM9866613, SRX34236540, BioSample SAMN61491943). This array is named IL71B on the core's sample sheet and its RNA library is named NL71B: the same piece under two names, because the array core and the sequencing core named the animals differently. Neither name has been changed. 33.05 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>205648300021_R06C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>205648300021_R06C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>treatment protocol</t>
+          <t>N2_EPIC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recurrent-arm tumors underwent diffusion-weighted-imaging-guided laser interstitial thermal therapy (DWI-LITT) using the Visualase system under real-time DWI-MRI guidance, performed ~24 h after a localizing MRI; ablation was stopped when it reached the tumor margins and animals were monitored longitudinally for recurrence. Primary-arm tumors were not ablated. Primary and recurrent tumors come from different animals (unpaired): rats 64, 67, 68 and 69 were not ablated; rats 65, 66, 70 and 71 were ablated and the tumor allowed to regrow.</t>
+          <t>U251N contralateral DNA methylation [N2 = RNA library N269B]</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>brain, contralateral hemisphere</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Homo sapiens; Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Contralateral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>contralateral hemisphere of rat 69 (sheet: 69B control N2)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>U251N</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>none (U251N implanted in the opposite hemisphere)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>205648300021</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>R07C01</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>N269B</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>GSM9866607</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SRX34236534</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>SAMN61491949</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>genomic DNA</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library N269B in GSE338105 (GSM9866607, SRX34236534, BioSample SAMN61491949). This array is named N2 on the core's sample sheet and its RNA library is named N269B: the same piece under two names, because the array core and the sequencing core named the animals differently. Neither name has been changed. 4.90 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>205648300021_R07C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>205648300021_R07C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>*extract protocol</t>
+          <t>C2B_EPIC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Genomic DNA was extracted from the same frozen pieces used for RNA (different aliquots). \PENDING{extraction kit and operator from the laboratory record}</t>
+          <t>U251N culture DNA methylation [C2B]</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>in vitro cell culture</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>U251N cultured cells (parental line)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>U251N</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>none (in vitro reference)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>205648300021</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>R08C01</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>C2B</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>GSM9866604</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SRX34236531</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>SAMN61491952</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>GSE338105</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>C2B</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>genomic DNA</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>DNA and RNA come from the same culture. Matched RNA-seq library C2B in GSE338105 (GSM9866604, SRX34236531, BioSample SAMN61491952). 86.19 % of that library's reads were assigned human.</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>205648300021_R08C01_Grn.idat</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>205648300021_R08C01_Red.idat</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>*label protocol</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bisulfite conversion and Infinium chemistry as performed by the core facility. \PENDING{kit, input mass and conversion protocol from the core}</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>*hybridization protocol</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip, standard protocol. \PENDING{core facility and instrument}</t>
-        </is>
-      </c>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>PROTOCOLS</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
+      <c r="D34" s="1" t="n"/>
+      <c r="E34" s="1" t="n"/>
+      <c r="F34" s="1" t="n"/>
+      <c r="G34" s="1" t="n"/>
+      <c r="H34" s="1" t="n"/>
+      <c r="I34" s="1" t="n"/>
+      <c r="J34" s="1" t="n"/>
+      <c r="K34" s="1" t="n"/>
+      <c r="L34" s="1" t="n"/>
+      <c r="M34" s="1" t="n"/>
+      <c r="N34" s="1" t="n"/>
+      <c r="O34" s="1" t="n"/>
+      <c r="P34" s="1" t="n"/>
+      <c r="Q34" s="1" t="n"/>
+      <c r="R34" s="1" t="n"/>
+      <c r="S34" s="1" t="n"/>
+      <c r="T34" s="1" t="n"/>
+      <c r="U34" s="1" t="n"/>
+      <c r="V34" s="1" t="n"/>
+      <c r="W34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>*scan protocol</t>
+          <t>growth protocol</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Illumina iScan. Chip 205648300021 scanned 2026-04-07.</t>
+          <t>Adult female immune-compromised RNU/RNU rats (Charles River Laboratories) were stereotactically implanted intracerebrally with log-growth-phase U251N human glioblastoma cells (5 x 10^4 cells in 10 uL PBS) under isoflurane anesthesia. A burr hole was drilled 3.50 mm right of bregma (anterio-posterior 0.0); cells were injected at a depth of 2.5 mm at 0.5 uL/10 s and the needle held in place 5 min before withdrawal. IACUC #1509. Tumor establishment was confirmed by MRI/DCE-MRI ~2 weeks after implantation. Eight implanted rats (64 to 71) contributed to this series.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>*data processing</t>
+          <t>treatment protocol</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IDATs were read with minfi; normalisation by noob; probes were filtered with the study's rat cross-hybridisation exclusion list before any human-compartment statistic. Copy number by conumee and DNAcopy against CopyNeutralIMA normals, with SeSAMe as an independent implementation; MGMT status by MGMT-STP27. The processed matrix supplied here is the noob beta matrix over all probes passing detection, with the matching detection P-value matrix.</t>
+          <t>Recurrent-arm tumors underwent diffusion-weighted-imaging-guided laser interstitial thermal therapy (DWI-LITT) using the Visualase system under real-time DWI-MRI guidance, performed ~24 h after a localizing MRI; ablation was stopped when it reached the tumor margins and animals were monitored longitudinally for recurrence. Primary-arm tumors were not ablated. Primary and recurrent tumors come from different animals (unpaired): rats 64, 67, 68 and 69 were not ablated; rats 65, 66, 70 and 71 were ablated and the tumor allowed to regrow.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>*genome build/assembly</t>
+          <t>*extract protocol</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hg19 (EPIC v1.0 manifest); copy-number segments lifted to hg38 where stated</t>
+          <t>Genomic DNA was extracted from the same frozen pieces used for RNA (different aliquots). \PENDING{extraction kit and operator from the laboratory record}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>*processed data files format and content</t>
+          <t>*label protocol</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U251N_EPIC_beta_noob.tsv.gz: probes (rows) by the eight arrays (columns), noob-normalised beta values. U251N_EPIC_detection_pvalues.tsv.gz: the same shape, detection P values.</t>
+          <t>Bisulfite conversion and Infinium chemistry as performed by the core facility. \PENDING{kit, input mass and conversion protocol from the core}</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>*hybridization protocol</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Illumina Infinium MethylationEPIC BeadChip, standard protocol. \PENDING{core facility and instrument}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
+        <is>
+          <t>*scan protocol</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Illumina iScan. Chip 205648300021 scanned 2026-04-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>*data processing</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>IDATs were read with minfi; normalisation by noob; probes were filtered with the study's rat cross-hybridisation exclusion list before any human-compartment statistic. Copy number by conumee and DNAcopy against CopyNeutralIMA normals, with SeSAMe as an independent implementation; MGMT status by MGMT-STP27. The processed matrix supplied here is the noob beta matrix over all probes passing detection, with the matching detection P-value matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>*genome build/assembly</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>hg19 (EPIC v1.0 manifest); copy-number segments lifted to hg38 where stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>*processed data files format and content</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>U251N_EPIC_beta_noob.tsv.gz: probes (rows) by the eight arrays (columns), noob-normalised beta values. U251N_EPIC_detection_pvalues.tsv.gz: the same shape, detection P values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t># The two file columns per sample are both required: GEO expects the Grn and Red IDAT of every array.</t>
         </is>

--- a/GEO/methylation/metadata_methylation.xlsx
+++ b/GEO/methylation/metadata_methylation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,7 +525,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eight arrays on a single EPIC BeadChip (sentrix 205648300021, positions R01C01-R08C01), scanned 2026-04-07. Six tumours: primary/pre-LITT (IL67B, IL68B, IL69B) against recurrent/post-LITT (IL66B, IL70B, IL71B; the matched RNA libraries are named NL70B and NL71B). One contralateral hemisphere (N2; RNA library N269B) and one in vitro parental culture (C2B). Each array has a matched RNA-seq library in GSE338105; DNA and RNA were taken from different aliquots of the same piece. No probe reached genome-wide significance between arms; the arrays are reported for copy number, MGMT status and tumour fraction.</t>
+          <t>Eight arrays on a single EPIC BeadChip (sentrix 205648300021, positions R01C01-R08C01), scanned 2022-04-07. Six tumours: primary/pre-LITT (IL67B, IL68B, IL69B) against recurrent/post-LITT (IL66B, IL70B, IL71B; the matched RNA libraries are named NL70B and NL71B). One contralateral hemisphere (N2; RNA library N269B) and one in vitro parental culture (C2B). Each array has a matched RNA-seq library in GSE338105; DNA and RNA were taken from different aliquots of the same piece. No probe reached genome-wide significance between arms; the arrays are reported for copy number, MGMT status and tumour fraction.</t>
         </is>
       </c>
     </row>
@@ -712,30 +712,60 @@
       </c>
       <c r="R24" s="1" t="inlineStr">
         <is>
+          <t>characteristics: plate well</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: dna volume ul</t>
+        </is>
+      </c>
+      <c r="T24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: qc ct HB-313</t>
+        </is>
+      </c>
+      <c r="U24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: qc ct HB-365</t>
+        </is>
+      </c>
+      <c r="V24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: detected probes at P&lt;0.05</t>
+        </is>
+      </c>
+      <c r="W24" s="1" t="inlineStr">
+        <is>
+          <t>characteristics: detected probes percent</t>
+        </is>
+      </c>
+      <c r="X24" s="1" t="inlineStr">
+        <is>
           <t>*molecule</t>
         </is>
       </c>
-      <c r="S24" s="1" t="inlineStr">
+      <c r="Y24" s="1" t="inlineStr">
         <is>
           <t>*description</t>
         </is>
       </c>
-      <c r="T24" s="1" t="inlineStr">
+      <c r="Z24" s="1" t="inlineStr">
         <is>
           <t>*platform</t>
         </is>
       </c>
-      <c r="U24" s="1" t="inlineStr">
+      <c r="AA24" s="1" t="inlineStr">
         <is>
           <t>raw file: Grn</t>
         </is>
       </c>
-      <c r="V24" s="1" t="inlineStr">
+      <c r="AB24" s="1" t="inlineStr">
         <is>
           <t>raw file: Red</t>
         </is>
       </c>
-      <c r="W24" s="1" t="inlineStr">
+      <c r="AC24" s="1" t="inlineStr">
         <is>
           <t>processed data file</t>
         </is>
@@ -829,30 +859,60 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>12.89</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>25.51</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>865256</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>99.930</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL66B in GSE338105 (GSM9866611, SRX34236538, BioSample SAMN61491945). 29.44 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>205648300021_R01C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>205648300021_R01C01_Red.idat</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -946,30 +1006,60 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12.84</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>25.64</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>865225</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>99.927</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL67B in GSE338105 (GSM9866608, SRX34236535, BioSample SAMN61491948). 42.52 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>205648300021_R02C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>205648300021_R02C01_Red.idat</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1063,30 +1153,60 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>12.61</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>24.88</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>865295</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>99.935</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL68B in GSE338105 (GSM9866609, SRX34236536, BioSample SAMN61491947). 45.38 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>205648300021_R03C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>205648300021_R03C01_Red.idat</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1180,30 +1300,60 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>11.94</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>24.13</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>865311</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>99.937</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library IL69B in GSE338105 (GSM9866610, SRX34236537, BioSample SAMN61491946). 64.40 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>205648300021_R04C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>205648300021_R04C01_Red.idat</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1297,30 +1447,60 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>12.85</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>23.99</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>865296</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>99.935</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library NL70B in GSE338105 (GSM9866612, SRX34236539, BioSample SAMN61491944). This array is named IL70B on the core's sample sheet and its RNA library is named NL70B: the same piece under two names, because the array core and the sequencing core named the animals differently. Neither name has been changed. 42.67 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>205648300021_R05C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>205648300021_R05C01_Red.idat</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1414,30 +1594,60 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>13.56</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>26.35</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>865257</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>99.930</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library NL71B in GSE338105 (GSM9866613, SRX34236540, BioSample SAMN61491943). This array is named IL71B on the core's sample sheet and its RNA library is named NL71B: the same piece under two names, because the array core and the sequencing core named the animals differently. Neither name has been changed. 33.05 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>205648300021_R06C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>205648300021_R06C01_Red.idat</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1531,30 +1741,60 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>G01</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>15.20</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>28.10</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>864815</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>99.879</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>DNA and RNA come from different aliquots of the same piece of tissue. Matched RNA-seq library N269B in GSE338105 (GSM9866607, SRX34236534, BioSample SAMN61491949). This array is named N2 on the core's sample sheet and its RNA library is named N269B: the same piece under two names, because the array core and the sequencing core named the animals differently. Neither name has been changed. 4.90 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>205648300021_R07C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>205648300021_R07C01_Red.idat</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1644,30 +1884,60 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>25.02</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>864965</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>99.897</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>genomic DNA</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>DNA and RNA come from the same culture. Matched RNA-seq library C2B in GSE338105 (GSM9866604, SRX34236531, BioSample SAMN61491952). 86.19 % of that library's reads were assigned human.</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>Illumina Infinium MethylationEPIC BeadChip (EPIC v1.0) (GPL21145)</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>205648300021_R08C01_Grn.idat</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>205648300021_R08C01_Red.idat</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>U251N_EPIC_beta_noob.tsv.gz</t>
         </is>
@@ -1704,6 +1974,12 @@
       <c r="U34" s="1" t="n"/>
       <c r="V34" s="1" t="n"/>
       <c r="W34" s="1" t="n"/>
+      <c r="X34" s="1" t="n"/>
+      <c r="Y34" s="1" t="n"/>
+      <c r="Z34" s="1" t="n"/>
+      <c r="AA34" s="1" t="n"/>
+      <c r="AB34" s="1" t="n"/>
+      <c r="AC34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1737,7 +2013,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Genomic DNA was extracted from the same frozen pieces used for RNA (different aliquots). \PENDING{extraction kit and operator from the laboratory record}</t>
+          <t>Genomic DNA was extracted by the laboratory from the same frozen pieces of tissue used for RNA, as separate aliquots. 45 uL of DNA per sample was submitted to the array core with no added water (plate 1724, one column of eight wells, A01 to H01). \PENDING{the DNA extraction kit, and the DNA mass corresponding to that 45 uL, from the laboratory record}</t>
         </is>
       </c>
     </row>
@@ -1749,7 +2025,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bisulfite conversion and Infinium chemistry as performed by the core facility. \PENDING{kit, input mass and conversion protocol from the core}</t>
+          <t>Bisulfite conversion and Infinium chemistry were performed by the array core on plate 1724 ("Raj-8"). The core checked each sample's DNA by qPCR before conversion; the per-sample Ct values for assays HB-313 and HB-365 are given in the sample characteristics. \PENDING{the bisulfite conversion kit and the DNA input mass, from the core}</t>
         </is>
       </c>
     </row>
@@ -1761,7 +2037,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Illumina Infinium MethylationEPIC BeadChip, standard protocol. \PENDING{core facility and instrument}</t>
+          <t>Illumina Infinium MethylationEPIC BeadChip v1.0, 8x5 format (SentrixDescriptor "BeadChip 8x5"); one chip, 205648300021, carrying the eight samples in column 1. Standard Infinium protocol. \PENDING{the name of the array core facility}</t>
         </is>
       </c>
     </row>
@@ -1773,7 +2049,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Illumina iScan. Chip 205648300021 scanned 2026-04-07.</t>
+          <t>Illumina iScan, scanner N141, iScan Control Software 3.4.8 (FPGA 4.0.20). Chip 205648300021 was decoded on 2021-07-11 and scanned on 2022-04-07 between 09:24 and 09:26; the instrument software extracted intensities with Extract Algorithm StandardWithBackground. Every value in this sentence is read from the RunInfo block of the deposited IDAT files themselves.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +2061,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IDATs were read with minfi; normalisation by noob; probes were filtered with the study's rat cross-hybridisation exclusion list before any human-compartment statistic. Copy number by conumee and DNAcopy against CopyNeutralIMA normals, with SeSAMe as an independent implementation; MGMT status by MGMT-STP27. The processed matrix supplied here is the noob beta matrix over all probes passing detection, with the matching detection P-value matrix.</t>
+          <t>The deposited matrices were built from the deposited IDATs with minfi 1.56.0 and IlluminaHumanMethylationEPICmanifest: detection P values by detectionP, normalisation by preprocessNoob, beta values by getBeta, over all 866,238 probes on the array. Column names are the array sample names. Per array, 864,815 to 865,311 probes pass detection at P &lt; 0.05 (99.879 to 99.937 %), as reported by the core and given per sample in the characteristics. In the study's own analyses, probes were then filtered with a rat cross-hybridisation exclusion list before any human-compartment statistic; copy number by conumee and DNAcopy against CopyNeutralIMA normals, with SeSAMe as an independent implementation; MGMT status by MGMT-STP27. sessionInfo_processed.txt records the exact versions used for the deposited matrices.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +2073,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hg19 (EPIC v1.0 manifest); copy-number segments lifted to hg38 where stated</t>
+          <t>hg19. The array core's own analysis used the EPIC v1.0 B4 manifest (IlluminaHumanMethylationEPICanno.ilm10b4.hg19); copy-number segments are lifted to hg38 where stated.</t>
         </is>
       </c>
     </row>
